--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/13B_Kreditaktenuebergabe_25-08-2025.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/13B_Kreditaktenuebergabe_25-08-2025.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabeliste" sheetId="1" r:id="R20b49b9162aa4ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabekontrolle" sheetId="2" r:id="Re675311b7c9b43ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabeliste" sheetId="1" r:id="Rc5eb8073c9ca4d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uebergabekontrolle" sheetId="2" r:id="R540c2f4e022f42ff"/>
   </x:sheets>
 </x:workbook>
 </file>
